--- a/Plantilla informe medico.xlsx
+++ b/Plantilla informe medico.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1750390c21b6fc84/Documentos/Escritorio/dvhenv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="8_{06FB2CC6-D408-4311-9208-0ABB8C952C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6038C793-3DF3-4D6A-A073-2F8BD0CE3480}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="8_{06FB2CC6-D408-4311-9208-0ABB8C952C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{396EF13C-E5C8-4E9C-8B95-5FF54EC067A0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{322BE1A8-1C11-470D-8D23-855D2E42EBED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IMAGEN" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -267,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -282,51 +283,52 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -390,25 +392,30 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>9923</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>72443</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>131491</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>569486</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>161162</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B58BE49-334D-4F16-B543-128E5E074073}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E87A48-B452-4F09-AE17-E956A83D56CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -424,8 +431,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2718594" y="15805548"/>
-          <a:ext cx="935646" cy="687115"/>
+          <a:off x="2679700" y="7397750"/>
+          <a:ext cx="937786" cy="681862"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -771,39 +778,39 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" spans="2:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="F7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="9" spans="2:8" ht="20" x14ac:dyDescent="0.4">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
@@ -815,145 +822,145 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11" t="s">
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="11" t="s">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="9"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="13"/>
+      <c r="C18" s="18"/>
     </row>
     <row r="20" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
     </row>
     <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
     </row>
     <row r="24" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
     </row>
     <row r="27" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="29" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
@@ -965,102 +972,102 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="13"/>
+      <c r="D31" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="16" t="s">
+      <c r="E31" s="16"/>
+      <c r="F31" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="17"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B40" s="6"/>
@@ -1068,32 +1075,61 @@
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="46" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-    </row>
-    <row r="47" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
+    <row r="46" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+    </row>
+    <row r="47" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="47">
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="B22:H23"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="B3:H4"/>
-    <mergeCell ref="B46:H47"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
@@ -1106,41 +1142,43 @@
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B22:H23"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26557374-E7CE-4043-BCB3-ACC6194363CF}">
+  <dimension ref="B3:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>